--- a/temps.xlsx
+++ b/temps.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D175EA79-D312-4E92-B456-011B2BA07F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6E9751-C507-4900-9F99-9D960038EB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4FD252C5-7EC1-44D5-8BE0-753F08B70FEF}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{4FD252C5-7EC1-44D5-8BE0-753F08B70FEF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="12">
   <si>
     <t>T</t>
   </si>
@@ -57,13 +57,31 @@
   </si>
   <si>
     <t>L = 1024</t>
+  </si>
+  <si>
+    <t>sigma = 2.50</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>plot</t>
+  </si>
+  <si>
+    <t>sigma = 1.20</t>
+  </si>
+  <si>
+    <t>sigma = 0.75</t>
+  </si>
+  <si>
+    <t>sigma = 1.80</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,8 +125,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -136,6 +161,11 @@
         <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -161,15 +191,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -185,12 +216,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="5" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -203,9 +228,22 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="6" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="60% - Accent1" xfId="2" builtinId="32"/>
+    <cellStyle name="Bad" xfId="6" builtinId="27"/>
     <cellStyle name="Good" xfId="4" builtinId="26"/>
     <cellStyle name="Neutral" xfId="5" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -522,43 +560,73 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73A8F25D-14CB-4B8D-B96A-E831A943DEF0}">
-  <dimension ref="E2:L20"/>
+  <dimension ref="E2:W32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="G2" s="8" t="s">
+    <row r="2" spans="5:23" x14ac:dyDescent="0.25">
+      <c r="F2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="8"/>
-    </row>
-    <row r="3" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="H2" s="15"/>
+    </row>
+    <row r="3" spans="5:23" x14ac:dyDescent="0.25">
       <c r="L3" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="W3" s="2"/>
+    </row>
+    <row r="4" spans="5:23" x14ac:dyDescent="0.25">
       <c r="L4" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="O4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="P4" s="15"/>
+      <c r="T4" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="U4" s="15"/>
+    </row>
+    <row r="5" spans="5:23" x14ac:dyDescent="0.25">
       <c r="E5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-    </row>
-    <row r="6" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="G5" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="O5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="V5" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="5:23" x14ac:dyDescent="0.25">
       <c r="E6">
         <v>1E-3</v>
       </c>
@@ -568,16 +636,18 @@
       <c r="G6" s="4">
         <v>0</v>
       </c>
-      <c r="H6" s="10">
-        <v>1</v>
-      </c>
-      <c r="I6" s="11">
+      <c r="H6" s="8">
+        <v>1</v>
+      </c>
+      <c r="I6" s="9">
         <v>2</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-    </row>
-    <row r="7" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="Q6" s="4"/>
+      <c r="V6" s="4"/>
+    </row>
+    <row r="7" spans="5:23" x14ac:dyDescent="0.25">
       <c r="E7">
         <v>2.8E-3</v>
       </c>
@@ -587,16 +657,23 @@
       <c r="G7" s="4">
         <v>0</v>
       </c>
-      <c r="H7" s="10">
-        <v>1</v>
-      </c>
-      <c r="I7" s="12" t="s">
+      <c r="H7" s="8">
+        <v>1</v>
+      </c>
+      <c r="I7" s="10" t="s">
         <v>4</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
-    </row>
-    <row r="8" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="P7" s="11"/>
+      <c r="Q7" s="13"/>
+      <c r="T7">
+        <v>0.1</v>
+      </c>
+      <c r="U7" s="11"/>
+      <c r="V7" s="13"/>
+    </row>
+    <row r="8" spans="5:23" x14ac:dyDescent="0.25">
       <c r="E8">
         <v>4.5999999999999999E-3</v>
       </c>
@@ -606,7 +683,7 @@
       <c r="G8" s="4">
         <v>0</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="8">
         <v>1</v>
       </c>
       <c r="I8" s="6" t="s">
@@ -614,8 +691,15 @@
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
-    </row>
-    <row r="9" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="P8" s="11"/>
+      <c r="Q8" s="13"/>
+      <c r="T8">
+        <v>0.2</v>
+      </c>
+      <c r="U8" s="11"/>
+      <c r="V8" s="13"/>
+    </row>
+    <row r="9" spans="5:23" x14ac:dyDescent="0.25">
       <c r="E9">
         <v>4.2000000000000003E-2</v>
       </c>
@@ -625,16 +709,23 @@
       <c r="G9" s="4">
         <v>0</v>
       </c>
-      <c r="H9" s="10">
-        <v>1</v>
-      </c>
-      <c r="I9" s="10">
+      <c r="H9" s="8">
+        <v>1</v>
+      </c>
+      <c r="I9" s="8">
         <v>2</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
-    </row>
-    <row r="10" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="P9" s="11"/>
+      <c r="Q9" s="13"/>
+      <c r="T9">
+        <v>0.4</v>
+      </c>
+      <c r="U9" s="11"/>
+      <c r="V9" s="13"/>
+    </row>
+    <row r="10" spans="5:23" x14ac:dyDescent="0.25">
       <c r="E10">
         <v>4.5999999999999999E-2</v>
       </c>
@@ -644,7 +735,7 @@
       <c r="G10" s="4">
         <v>0</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="8">
         <v>1</v>
       </c>
       <c r="I10" s="6" t="s">
@@ -652,8 +743,10 @@
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
-    </row>
-    <row r="11" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="Q10" s="4"/>
+      <c r="V10" s="4"/>
+    </row>
+    <row r="11" spans="5:23" x14ac:dyDescent="0.25">
       <c r="E11">
         <v>0.17</v>
       </c>
@@ -663,7 +756,7 @@
       <c r="G11" s="4">
         <v>0</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="8">
         <v>1</v>
       </c>
       <c r="I11" s="6" t="s">
@@ -671,8 +764,18 @@
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
-    </row>
-    <row r="12" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="O11">
+        <v>1.19333333</v>
+      </c>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="13"/>
+      <c r="T11">
+        <v>0.8</v>
+      </c>
+      <c r="U11" s="11"/>
+      <c r="V11" s="13"/>
+    </row>
+    <row r="12" spans="5:23" x14ac:dyDescent="0.25">
       <c r="E12">
         <v>0.25</v>
       </c>
@@ -682,16 +785,26 @@
       <c r="G12" s="4">
         <v>0</v>
       </c>
-      <c r="H12" s="10">
-        <v>1</v>
-      </c>
-      <c r="I12" s="9" t="s">
+      <c r="H12" s="8">
+        <v>1</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>4</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
-    </row>
-    <row r="13" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="O12">
+        <v>1.26666667</v>
+      </c>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="13"/>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12" s="11"/>
+      <c r="V12" s="13"/>
+    </row>
+    <row r="13" spans="5:23" x14ac:dyDescent="0.25">
       <c r="E13">
         <v>0.33</v>
       </c>
@@ -701,16 +814,23 @@
       <c r="G13" s="4">
         <v>0</v>
       </c>
-      <c r="H13" s="10">
-        <v>1</v>
-      </c>
-      <c r="I13" s="9" t="s">
+      <c r="H13" s="8">
+        <v>1</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>4</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
-    </row>
-    <row r="14" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="P13" s="11"/>
+      <c r="Q13" s="13"/>
+      <c r="T13">
+        <v>1.2</v>
+      </c>
+      <c r="U13" s="11"/>
+      <c r="V13" s="13"/>
+    </row>
+    <row r="14" spans="5:23" x14ac:dyDescent="0.25">
       <c r="E14">
         <v>0.49</v>
       </c>
@@ -720,13 +840,16 @@
       <c r="G14" s="4">
         <v>0</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="7" t="s">
         <v>4</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
-    </row>
-    <row r="15" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="R14" s="4"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+    </row>
+    <row r="15" spans="5:23" x14ac:dyDescent="0.25">
       <c r="E15">
         <v>0.56999999999999995</v>
       </c>
@@ -736,13 +859,16 @@
       <c r="G15" s="4">
         <v>0</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="7" t="s">
         <v>4</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
-    </row>
-    <row r="16" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="R15" s="4"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+    </row>
+    <row r="16" spans="5:23" x14ac:dyDescent="0.25">
       <c r="E16">
         <v>0.69</v>
       </c>
@@ -752,13 +878,16 @@
       <c r="G16" s="4">
         <v>0</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="7" t="s">
         <v>4</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
-    </row>
-    <row r="17" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="R16" s="4"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+    </row>
+    <row r="17" spans="5:22" x14ac:dyDescent="0.25">
       <c r="E17">
         <v>0.77</v>
       </c>
@@ -768,13 +897,16 @@
       <c r="G17" s="4">
         <v>0</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="8">
         <v>1</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
-    </row>
-    <row r="18" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="R17" s="4"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+    </row>
+    <row r="18" spans="5:22" x14ac:dyDescent="0.25">
       <c r="E18">
         <v>0.85</v>
       </c>
@@ -784,13 +916,16 @@
       <c r="G18" s="4">
         <v>0</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="8">
         <v>1</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
-    </row>
-    <row r="19" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="R18" s="4"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+    </row>
+    <row r="19" spans="5:22" x14ac:dyDescent="0.25">
       <c r="E19">
         <v>0.93</v>
       </c>
@@ -800,14 +935,21 @@
       <c r="G19" s="4">
         <v>0</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="8">
         <v>1</v>
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
-    </row>
-    <row r="20" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="O19" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="P19" s="15"/>
+      <c r="R19" s="4"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+    </row>
+    <row r="20" spans="5:22" x14ac:dyDescent="0.25">
       <c r="E20">
         <v>1.05</v>
       </c>
@@ -817,17 +959,116 @@
       <c r="G20" s="4">
         <v>0</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="8">
         <v>1</v>
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
+      <c r="O20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q20" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="4"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+    </row>
+    <row r="21" spans="5:22" x14ac:dyDescent="0.25">
+      <c r="Q21" s="4"/>
+    </row>
+    <row r="22" spans="5:22" x14ac:dyDescent="0.25">
+      <c r="O22">
+        <v>0.2</v>
+      </c>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="13"/>
+    </row>
+    <row r="23" spans="5:22" x14ac:dyDescent="0.25">
+      <c r="E23" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="15"/>
+      <c r="O23">
+        <v>0.3</v>
+      </c>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="13"/>
+    </row>
+    <row r="24" spans="5:22" x14ac:dyDescent="0.25">
+      <c r="E24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24">
+        <v>0.4</v>
+      </c>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="13"/>
+    </row>
+    <row r="25" spans="5:22" x14ac:dyDescent="0.25">
+      <c r="G25" s="4"/>
+      <c r="Q25" s="4"/>
+    </row>
+    <row r="26" spans="5:22" x14ac:dyDescent="0.25">
+      <c r="F26" s="11"/>
+      <c r="G26" s="13"/>
+      <c r="O26">
+        <v>1.85</v>
+      </c>
+      <c r="P26" s="11"/>
+      <c r="Q26" s="13"/>
+    </row>
+    <row r="27" spans="5:22" x14ac:dyDescent="0.25">
+      <c r="F27" s="11"/>
+      <c r="G27" s="13"/>
+      <c r="O27">
+        <v>1.95</v>
+      </c>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="13"/>
+    </row>
+    <row r="28" spans="5:22" x14ac:dyDescent="0.25">
+      <c r="F28" s="11"/>
+      <c r="G28" s="13"/>
+      <c r="O28">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P28" s="11"/>
+      <c r="Q28" s="13"/>
+    </row>
+    <row r="29" spans="5:22" x14ac:dyDescent="0.25">
+      <c r="G29" s="4"/>
+    </row>
+    <row r="30" spans="5:22" x14ac:dyDescent="0.25">
+      <c r="F30" s="11"/>
+      <c r="G30" s="13"/>
+    </row>
+    <row r="31" spans="5:22" x14ac:dyDescent="0.25">
+      <c r="F31" s="11"/>
+      <c r="G31" s="13"/>
+    </row>
+    <row r="32" spans="5:22" x14ac:dyDescent="0.25">
+      <c r="F32" s="11"/>
+      <c r="G32" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="6">
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="E23:F23"/>
     <mergeCell ref="G5:K5"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="O4:P4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
